--- a/output/pdf_financials_xlsx/NXG.xlsx
+++ b/output/pdf_financials_xlsx/NXG.xlsx
@@ -958,10 +958,10 @@
         <v>11.125195</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>10.517719</v>
+        <v>12.095201</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>10.776676</v>
+        <v>12.998338</v>
       </c>
     </row>
     <row r="11">
@@ -1016,10 +1016,10 @@
         <v>-0.305055</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>2.604201</v>
+        <v>1.026719</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>4.157238</v>
+        <v>1.935576</v>
       </c>
     </row>
     <row r="12">
@@ -2372,55 +2372,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.410297</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.166176</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.166176</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.014728</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.354784</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.969865</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.302948</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.302948</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.681353</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.026993</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.833658</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.527092</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.317023</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.766891</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.876765</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.705666</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.77667</v>
       </c>
     </row>
     <row r="35">
@@ -2488,55 +2488,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.410297</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.166176</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.166176</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.014728</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.354784</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.969865</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.302948</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.302948</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.681353</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.026993</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.833658</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.527092</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.317023</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.766891</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.876765</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.705666</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.77667</v>
       </c>
     </row>
     <row r="37">
@@ -3184,55 +3184,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.531741</v>
+        <v>0.121444</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.250227</v>
+        <v>0.084051</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.250227</v>
+        <v>0.084051</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.146723</v>
+        <v>0.131995</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.475342</v>
+        <v>0.120558</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.085741</v>
+        <v>0.115876</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.412864</v>
+        <v>0.109916</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.093502</v>
+        <v>5.790554</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.422554</v>
+        <v>6.741201</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.576432</v>
+        <v>6.549439</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>11.762032</v>
+        <v>10.928374</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>14.148039</v>
+        <v>13.620947</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>20.351555</v>
+        <v>18.034532</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>17.593788</v>
+        <v>15.826897</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>22.614751</v>
+        <v>20.737986</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>23.830438</v>
+        <v>22.124772</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>31.675086</v>
+        <v>26.898416</v>
       </c>
     </row>
     <row r="49">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -34024,7 +34024,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E277" s="5" t="n">
@@ -58570,7 +58570,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -59126,7 +59126,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">

--- a/output/pdf_financials_xlsx/NXG.xlsx
+++ b/output/pdf_financials_xlsx/NXG.xlsx
@@ -2081,49 +2081,49 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.00265</v>
+        <v>0.05884</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.00144</v>
+        <v>0.0532</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.011167</v>
+        <v>0.07334400000000001</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.015007</v>
+        <v>0.06360300000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.022669</v>
+        <v>0.06403</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.040708</v>
+        <v>0.033769</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.041477</v>
+        <v>0.033738</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.088573</v>
+        <v>0.129948</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.264163</v>
+        <v>0.31713</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.5669729999999999</v>
+        <v>0.83275</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.020261</v>
+        <v>1.334968</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1.136073</v>
+        <v>1.405523</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.121014</v>
+        <v>1.307547</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.05361</v>
+        <v>1.266452</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.978256</v>
+        <v>1.222055</v>
       </c>
     </row>
     <row r="29">
@@ -2139,49 +2139,49 @@
         <v>-2.044993</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.8043670000000001</v>
+        <v>-0.748177</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.6148130000000001</v>
+        <v>-0.563053</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.534859</v>
+        <v>0.597036</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.623556</v>
+        <v>0.672152</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.454947</v>
+        <v>-0.413586</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.147617</v>
+        <v>-0.154556</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.629281</v>
+        <v>0.621542</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.537334</v>
+        <v>-0.495959</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.456799</v>
+        <v>-0.403832</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.286087</v>
+        <v>0.551864</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>3.030135</v>
+        <v>3.344842</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.27054</v>
+        <v>1.53999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.815959</v>
+        <v>1.002492</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.080329</v>
+        <v>2.293171</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.913832</v>
+        <v>3.157631</v>
       </c>
     </row>
     <row r="30">
@@ -2197,49 +2197,49 @@
         <v>-69.5357309471445</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-22.8231110788278</v>
+        <v>-21.22877589163174</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-15.55022949255676</v>
+        <v>-14.2410836570999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>12.16765857330604</v>
+        <v>13.58214072114771</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12.69837778791928</v>
+        <v>13.68800881862338</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-10.78992904854468</v>
+        <v>-9.80897466182083</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-3.14612761832745</v>
+        <v>-3.294016950474657</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.9350107459317</v>
+        <v>10.8005302067723</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-9.474200174555456</v>
+        <v>-8.744681788928952</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-6.371439263578288</v>
+        <v>-5.632654757758548</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2.998824943893954</v>
+        <v>5.784756136549696</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>25.58957701046998</v>
+        <v>28.24728665450695</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>9.940672367318696</v>
+        <v>12.04884225521992</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5.892962676244368</v>
+        <v>7.240128412375584</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.62696744687771</v>
+        <v>13.91885397315713</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>16.2489595660865</v>
+        <v>17.60850263282896</v>
       </c>
     </row>
     <row r="31">
@@ -6307,49 +6307,49 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.05884</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.0532</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.07334400000000001</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.06360300000000001</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.06403</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.074477</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.033738</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.129948</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.31713</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.83275</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>1.334968</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.405523</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.307547</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.266452</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>1.222055</v>
       </c>
     </row>
     <row r="101">
@@ -37882,7 +37882,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -37969,7 +37973,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -47795,7 +47799,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -47892,7 +47896,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -49498,7 +49506,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -49595,7 +49603,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -50476,7 +50488,11 @@
           <t>Additions of intangible assets (note 7)</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -53214,7 +53230,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -53313,7 +53329,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -58657,7 +58677,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -58746,7 +58766,11 @@
           <t>Depreciation of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -62694,7 +62718,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>
@@ -63939,7 +63967,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -64032,7 +64060,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E565" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NXG.xlsx
+++ b/output/pdf_financials_xlsx/NXG.xlsx
@@ -760,34 +760,34 @@
         <v>0.420754</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.427344</v>
+        <v>1.656371</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.604588</v>
+        <v>1.801563</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.580615</v>
+        <v>1.814563</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2.316811</v>
+        <v>2.583043</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>3.413716</v>
+        <v>3.733224</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>4.671038</v>
+        <v>5.070243</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4.898446</v>
+        <v>5.378184</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>6.76128</v>
+        <v>7.249391</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>7.738816</v>
+        <v>8.236608</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>7.90531</v>
+        <v>8.398103000000001</v>
       </c>
     </row>
     <row r="8">
@@ -46993,7 +46993,11 @@
           <t>Net cash (used in) / generated from operating activities</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -48492,7 +48496,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -58201,7 +58209,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
